--- a/data/age_indexes/excel_files/a1_max_age_indexes.xlsx
+++ b/data/age_indexes/excel_files/a1_max_age_indexes.xlsx
@@ -7,12 +7,13 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="run1" sheetId="1" r:id="rId1"/>
-    <sheet name="run2" sheetId="2" r:id="rId2"/>
-    <sheet name="run3" sheetId="3" r:id="rId3"/>
-    <sheet name="run4" sheetId="4" r:id="rId4"/>
-    <sheet name="run5" sheetId="5" r:id="rId5"/>
-    <sheet name="best" sheetId="6" r:id="rId6"/>
+    <sheet name="run0" sheetId="1" r:id="rId1"/>
+    <sheet name="run1" sheetId="2" r:id="rId2"/>
+    <sheet name="run2" sheetId="3" r:id="rId3"/>
+    <sheet name="run3" sheetId="4" r:id="rId4"/>
+    <sheet name="run4" sheetId="5" r:id="rId5"/>
+    <sheet name="run5" sheetId="6" r:id="rId6"/>
+    <sheet name="best" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -367,7 +368,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -389,7 +390,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZIC1, RUNX1, PITX1, PAX8</t>
+          <t>PITX1, NANOG, DBP</t>
         </is>
       </c>
     </row>
@@ -406,7 +407,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PTTG1, ETV4, NR2F2, PITX1</t>
+          <t>BHLHE41, CBX8, PITX1</t>
         </is>
       </c>
     </row>
@@ -418,12 +419,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JUND, RELB</t>
+          <t>DDIT3, BRIP1</t>
         </is>
       </c>
     </row>
@@ -440,7 +441,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DBP, LHX2, SLA2</t>
+          <t>ASCL1, HNF1A, AES</t>
         </is>
       </c>
     </row>
@@ -452,12 +453,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MXD1, POU5F1, LIMD1, PAX2</t>
+          <t>HLX, EN1</t>
         </is>
       </c>
     </row>
@@ -469,12 +470,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PRDM1, ZFP36, TEAD4</t>
+          <t>ETS2, GATA1, NR1I2</t>
         </is>
       </c>
     </row>
@@ -486,12 +487,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOTCH3, FOXP1, SIX1</t>
+          <t>HOXB7, CREB5, RUNX1</t>
         </is>
       </c>
     </row>
@@ -508,7 +509,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>THRA, EAF1, TEAD4, MAFF</t>
+          <t>BARD1, DLX4, NOTCH3</t>
         </is>
       </c>
     </row>
@@ -520,12 +521,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HLF, TLX1, ZBTB16, GATA6</t>
+          <t>BARD1, CEBPD, E2F8</t>
         </is>
       </c>
     </row>
@@ -537,12 +538,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HIF3A, DLX5, ATRX, TBX5, ETV7, MAFB</t>
+          <t>HLF, GLI3, HIF3A</t>
         </is>
       </c>
     </row>
@@ -559,7 +560,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RUNX1, NR0B2</t>
+          <t>FOXJ1</t>
         </is>
       </c>
     </row>
@@ -571,12 +572,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RUNX3, GATA1, STAT5A, RELA</t>
+          <t>GLI1, NUPR1</t>
         </is>
       </c>
     </row>
@@ -593,7 +594,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STAT1, ETS1, STAT5A</t>
+          <t>ID3, EOMES</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HLTF, KLF4, FOXC1, GFI1</t>
+          <t>TWIST1, CDX2</t>
         </is>
       </c>
     </row>
@@ -627,7 +628,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEAT1, CREB5, NPAS2, UTF1</t>
+          <t>SPI1, ANKRD1, REL</t>
         </is>
       </c>
     </row>
@@ -644,7 +645,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MED15, UTF1</t>
+          <t>MED15, MAFB</t>
         </is>
       </c>
     </row>
@@ -656,12 +657,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MEF2B, TEAD1, XBP1, OTX2, FOSL2</t>
+          <t>BCL6, E2F8</t>
         </is>
       </c>
     </row>
@@ -678,7 +679,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NFIC, NFE2, IRF2, SPI1</t>
+          <t>NFE2, SPI1</t>
         </is>
       </c>
     </row>
@@ -695,7 +696,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOX2, CDX2, NUPR1</t>
+          <t>SALL4, HOXA10</t>
         </is>
       </c>
     </row>
@@ -712,7 +713,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NFIC, ZFP36, HOPX, TCF7, NANOG</t>
+          <t>EOMES, ETV7, FOXG1</t>
         </is>
       </c>
     </row>
@@ -724,12 +725,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RUNX1, SPDEF, HSF4, NR5A2, TP63</t>
+          <t>PAX3, CBX7</t>
         </is>
       </c>
     </row>
@@ -741,12 +742,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MYF6, GATA4, RARA</t>
+          <t>GATA4, GATA1</t>
         </is>
       </c>
     </row>
@@ -763,7 +764,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HOXA4, NR1H3</t>
+          <t>CRABP2</t>
         </is>
       </c>
     </row>
@@ -775,12 +776,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEY1, MSX1, KCNIP3, NFIL3</t>
+          <t>SOX2, NFIL3</t>
         </is>
       </c>
     </row>
@@ -797,7 +798,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NANOG, VDR, JUND, FOXH1, HOXA10</t>
+          <t>HOXA10, CREB5</t>
         </is>
       </c>
     </row>
@@ -809,12 +810,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RELB, MXD1, CDX1</t>
+          <t>ASCL1, EBF1</t>
         </is>
       </c>
     </row>
@@ -826,12 +827,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MEF2B, ETV7, GLI1, FOXN4</t>
+          <t>TP63, GLI1, NANOG</t>
         </is>
       </c>
     </row>
@@ -848,7 +849,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KLF5, CDX1, RUNX1, REL</t>
+          <t>RUNX1, MXD1</t>
         </is>
       </c>
     </row>
@@ -865,7 +866,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IRF5, CEBPG, FOSL2, NR2C2</t>
+          <t>FOSL2, ETS2</t>
         </is>
       </c>
     </row>
@@ -877,12 +878,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KLF6, NFIL3, KLF9</t>
+          <t>EAF1, DBP</t>
         </is>
       </c>
     </row>
@@ -894,12 +895,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CREB5, RELB, SALL4</t>
+          <t>EOMES, GLIS3, SLA2</t>
         </is>
       </c>
     </row>
@@ -911,12 +912,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CDX1, NOTCH3, FOXO1, NR1H4, SOX4, GLI1</t>
+          <t>EOMES, HOXA1, FOXF2</t>
         </is>
       </c>
     </row>
@@ -933,7 +934,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZNF300, PAWR, GLI3, E2F8</t>
+          <t>ETS2, AHR, GATA1</t>
         </is>
       </c>
     </row>
@@ -945,12 +946,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FOXJ1, NAB2, PAX2, CREB5</t>
+          <t>CIITA, HMGA1</t>
         </is>
       </c>
     </row>
@@ -967,7 +968,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LHX4, BHLHE41, NAB2, FOXP2</t>
+          <t>MEF2B, FOXQ1</t>
         </is>
       </c>
     </row>
@@ -979,12 +980,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CRABP2, KLF12, ETV7, FOSL2, EOMES, ATF5</t>
+          <t>HLX, NFIL3, ONECUT2</t>
         </is>
       </c>
     </row>
@@ -996,12 +997,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GATA1, BRCA1, CREM</t>
+          <t>BACH1, HIF3A, HOXA1</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1014,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ABL1, MSX2, NR1H4, SMAD3, CRX</t>
+          <t>GATA6, EOMES</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1036,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SPIB, CDX1, HIF3A, CREB5</t>
+          <t>HEY1, SPDEF</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1048,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GATA1, ZFP36, PITX1</t>
+          <t>EIF2AK2, NAB2</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1070,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GATA2, FOXG1, PAX8, GLI1</t>
+          <t>HOXA4, PAX8, CEBPD</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1082,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EGR1, PGR, FOS, IRF1</t>
+          <t>EOMES, DLX5</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1104,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HDAC7, HDAC9, POLR1A, CREM, PGR, RFX5</t>
+          <t>SRF, CEBPD, NOTCH3</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1116,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HIVEP2, FOSL2, ELF3, LMO3, POU1F1</t>
+          <t>MAFF, ASXL1, ETV7</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1133,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JUNB, DDIT3, NR1D1</t>
+          <t>BARX2, ETV7, AES</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1155,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E2F8, EIF2AK2, SIX1</t>
+          <t>BHLHE41, E2F8, FOXP2</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1167,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MLXIPL, MSX1, ONECUT1</t>
+          <t>FOXF1, FOXN1, HOXD3</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1184,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JUND, HES1, POU5F1, ABL1</t>
+          <t>JUND, ARNT</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1211,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1227,12 +1228,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RFX2, POU4F1, DBP, DLX4</t>
+          <t>IRF1, PITX1</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1250,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROX1, CBX8, PITX1</t>
+          <t>DLX3, HES6, MCM2</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1267,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NFRKB, JUND, FOXH1</t>
+          <t>CREB5, FOXL2, BATF</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIX1, DLX4, NANOG, TOP2B</t>
+          <t>RUNX3, CDX2, ETS2</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1296,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GATA6, FOXF1, POU5F1, NANOG, LIMD1</t>
+          <t>HOXC6, SHOX, ONECUT2, PITX2</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1318,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>POU5F1, GATA1, TAL1</t>
+          <t>CIITA, GATA1, ETV7, RUNX1</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1330,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RBPJ, JUNB, GATA3, PITX1</t>
+          <t>KAT5, ZEB2, HOXA1, ZFHX3</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1352,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TRAF6, NRF1, POU5F1, CIITA, RUNX3</t>
+          <t>NFATC3, DLX4, PLAGL2</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1364,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GFI1, ZNF383, NEAT1</t>
+          <t>BRD7, REL, ZNF383</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1381,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NKX2-3, NR0B2, LYL1, GATA3, CDX2, RUNX1</t>
+          <t>POU1F1, BARX2, ZBTB16, LYL1</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1403,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NR0B2, TP63</t>
+          <t>IFI16, NR0B2, NUPR1</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DDIT3, NUPR1, PIR</t>
+          <t>NFKB2, WWTR1, PIR</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1432,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MYOD1, FOXE1, WWTR1, EIF2AK2, DLX4</t>
+          <t>E2F7, GLI1, FLI1</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1454,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FOXO1, TWIST1, CDX2</t>
+          <t>NCOA4, TWIST1, CDX2</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1466,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LYL1, HNF1A, SPI1, HOXA5</t>
+          <t>YEATS4, SPI1, REL</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1483,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FLI1, HOXB7, CEBPE, SIX1</t>
+          <t>PAX8, HIF3A, CEBPE, SFPQ</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1505,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TIAL1, FOSL2, KLF11, MXD1</t>
+          <t>CBFB, BCL6, E2F8</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1517,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RARG, KLF6, CEBPE</t>
+          <t>PRDM1, ONECUT1, SPI1</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1534,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TRIM22, HOXA1, FOXH1</t>
+          <t>TOP2B, TBX5, RORC</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1551,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LIMD1, FOXF1, ZFP36</t>
+          <t>RARB, JUND, NR4A1, HEYL, EGR1</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1568,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LEF1, RUNX3, SATB2, STAT5A, NR0B2</t>
+          <t>CNBP, SATB1, AES</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1585,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MYF6, GATA4, TFDP3, LMO2</t>
+          <t>NKX2-5, GATA4, OTX2, CEBPD</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1602,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>POU5F1, CREB5, ETV4, PPARG</t>
+          <t>TBX21, FIGLA, NOTCH3, TFAP2A, PPARG, POU5F1</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1624,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FOXP1, MEF2D, NFATC2</t>
+          <t>ZFP36, HEYL, GLI1</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1636,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MTA3, CREB5, CDX1, EOMES</t>
+          <t>MEF2B, ZFP36, ARNTL2, HOXA10</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DDIT3, SOX17, NR0B1, KLF2, E2F5</t>
+          <t>HAND2, PITX1, FOXG1, NR0B1, FOXH1</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1675,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ZFHX3, GATA1, ETS2, JUND</t>
+          <t>DLX4, ZNF224, NKX2-5</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1687,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PER1, HOXA1, RUNX1, PITX1, REL</t>
+          <t>IRF6, TFAP2A, RARA, RUNX1</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1709,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DDB1, FOSL2</t>
+          <t>GATA3, FOSL2, LMO3</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HOXA5, TEAD1, EBF3</t>
+          <t>HOXC11, ONECUT1, HOXA5, DBP</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1738,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SLA2, HLX, HOXC6</t>
+          <t>FHL2, IRF1</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1760,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RUNX1, PIAS2, ETV4, CDX2, BRIP1, GATA2</t>
+          <t>LMX1B, GCM1, HEY2, KDM4C, HOXA1</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1777,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BARD1, NR2F1, TWIST2, NR5A2</t>
+          <t>DDIT3, SREBF2, CEBPD, TFAP2A, PLAG1, LEF1</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1789,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ATF3, CREB5, EGR1</t>
+          <t>PAX2, EOMES, HOXA4</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1806,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TFAP2A, FOXH1, HNF4A, FOS</t>
+          <t>TBX5, OTX1, HOXA4, FOXQ1, PITX2</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1823,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ATF5, CIITA, HSF4</t>
+          <t>FOXF1, ATF5, CDX1</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BACH1, HOXA1, HIF3A</t>
+          <t>HOXA1, KLF15, BACH1, HIF3A</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1862,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PROX1, VDR, JUN, EGR1</t>
+          <t>TOP2B, MAML1, NKX2-5</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1874,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEY1, SPDEF</t>
+          <t>ELF3</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1896,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FOS, HNF4A, PITX1</t>
+          <t>PITX1, UHRF1, GATA1</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1908,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PAX8, RELB, FOXF1</t>
+          <t>CREB5, HLX, TEAD4, DLX3</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1930,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SPI1, OTX1, NUPR1, NANOG, JUN</t>
+          <t>FOXG1, CDX2, DLX5</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1942,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZEB1, MLLT10, BHLHE41</t>
+          <t>DDIT3, RUNX1T1, TP63</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1959,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HOXA11, MAFF, ETV7, LHX3</t>
+          <t>SHOX, BTAF1, EGR1, MITF, SOX6, NR4A1</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1976,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FOXJ1, SLA2, DDIT3, SOX2, JUND</t>
+          <t>SP7, PAX2, KLF1, FOXQ1</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1993,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IRF3, RBL1, KLF2, ZFP36</t>
+          <t>ONECUT2, FOSB, TFAP2B, HLX, E2F8, SHOX</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2010,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CIITA, MAF, REST</t>
+          <t>MSX1, FOXF1, FOXN1</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2032,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PPARA, DDIT3, NAB2, ZNF76, JUND, HLTF</t>
+          <t>SLC2A4RG, MAFF, ZNF143</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2054,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2070,12 +2071,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TNFAIP3, NANOG</t>
+          <t>NR4A2, DLX4, FOXL1</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2093,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HAND2, MCM2, EN1, SMURF2</t>
+          <t>POU2AF1, HLF, CRX</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2105,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PPARD, KLF6</t>
+          <t>STAT4, PAX5, FOXG1, MEF2C, NAB2</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2122,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FOXA1, HNF1A, NFATC2, LHX2</t>
+          <t>SPIB, PRDM1, CDX2, ETS2</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2139,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HOXD3, NR1I2, KLF2, ETV4</t>
+          <t>LMX1B, KLF12, POU5F1, GATA1</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2161,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BIN1, POU5F1, TAL1, GATA1</t>
+          <t>NHLH2, ZNF383, ETV7, GFI1</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2173,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BTAF1, HOXA1, ZNF335, ETV7</t>
+          <t>NFKB1, ETS1, STAT3, ESR1</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2190,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NFKBIA, RUNX3, TFAP2A, PROX1</t>
+          <t>NFKBIA, KLF6, CNBP, RUNX3</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2207,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CBFB, GLI2, TBR1, IKZF1, GATA2</t>
+          <t>HDAC10, E2F8, HLX, FOSL2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2229,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>POU2F3, MAFB, ZBTB16, ETV7, NR0B2, TFAP2C</t>
+          <t>KLF15, TOP2B, TFAP2C, TBX5</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2241,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TLE3, SIX1, CEBPE</t>
+          <t>HIF3A, TBX5, NR4A2, NR0B2, MAFB</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2263,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CRABP2, GLI1, NANOG</t>
+          <t>TOB1, WWTR1, HNF1A</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2275,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GLIS3, DLX4, WWTR1, SHOX2</t>
+          <t>ETS2, EPAS1, TFAP2A, FOXO4, GATA1</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2292,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RELB, GFI1, ZBTB16</t>
+          <t>KLF15, HOXB7, TWIST1, TP63</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2309,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MEF2B, MSX1, UTF1, CREB5</t>
+          <t>KLF2, NCOA1, SPI1, CEBPD</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2326,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HOXB7, NUPR1, LYL1</t>
+          <t>POU2F3, SPI1, UHRF1, CEBPD</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2343,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KLF15, GRHL1, DDIT3, BCL6, STAT5A, ELL</t>
+          <t>CEBPD, SLA2, ELL, NFKBIA, NFATC1</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2365,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TRAF6, RUNX3, KLF2, SPI1</t>
+          <t>CNBP, ESRRA, PPARA, SPI1, MSC</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2382,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FOXC2, NUPR1, REL</t>
+          <t>HDAC4, IRF1, PAX8</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2394,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IRF2, EGR1, JUND, FOXM1</t>
+          <t>RARB, ZFP36, DLX3</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2411,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ETV7, TP63, FOXL2, STAT5A</t>
+          <t>COPS5, RUNX1, SMAD7, STAT5A</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2433,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TBX21, PAX2, GATA1</t>
+          <t>LHX2, TBX21, PAX2, HNF1A</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2450,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CREB5, BRIP1, HOXC6, POU3F2</t>
+          <t>HSF4, TBX5, HOXC6, ZIC1</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2462,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TFAP2A, IRF3, MITF, PITX1</t>
+          <t>NFATC2, NFIC</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2479,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CREB5, MSX1, SIX1</t>
+          <t>MCM2, CREB5, FOXP1, CDX1</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2501,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NFKB2, CDX1</t>
+          <t>ONECUT2, CREM, KLF2, SOX17</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2518,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TFCP2L1, EED, EOMES, EAF1, SIX1</t>
+          <t>BARD1, GLI1, FOXH1, EOMES</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2535,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VDR, RUNX3, GATA6, HNF4A, RUNX2, RUNX1</t>
+          <t>ETV7, PRDM1, NHLH2, HOXA1</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2547,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GATA1, HOXB7, HEYL</t>
+          <t>SP1, PITX1, POU2F2</t>
         </is>
       </c>
     </row>
@@ -2563,12 +2564,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E2F3, SOX9, CRTC1, NANOG, HOPX</t>
+          <t>HOXA5, TEAD1, PAX2</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2586,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SOX4, HOXD3, MSC</t>
+          <t>ETV7, HEY1, SALL4, HOXD3</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2603,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENO1, NCOA4, NR1I2, GLI1, CDX2</t>
+          <t>ZEB2, FOXG1, NR1H4</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2620,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MEF2A, ZNF300, LEF1, ERG</t>
+          <t>HLTF, GATA1, ERG, NR2C2, MEF2A</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2632,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ETS2, EGR1, TFAP2A</t>
+          <t>TFAP2B, HOXA4, PAX2</t>
         </is>
       </c>
     </row>
@@ -2648,12 +2649,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LMO3, NAB2, PLAG1, PITX2, HLF</t>
+          <t>NR0B2, HNF4A, SOX2, NR1I2, DLX4</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2666,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>POU2F3, NFIL3, FOSL2</t>
+          <t>TOP2B, HLX, ZIC2, TFAP2C, SIX1</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2683,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NKX2-2, HOXA1, KHSRP</t>
+          <t>MYC, TWIST1, BRCA1</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2705,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AHR, GLI2, IRF8, EGR1, CEBPB</t>
+          <t>MSC, ZNF383, NR1H4</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2717,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NR5A1, KLF2, SPDEF</t>
+          <t>RARG, SPDEF, CREB5</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2739,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FOXA1, NANOG, SIX1, PITX1</t>
+          <t>HNF1A, CDX1, PITX1</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2756,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RELB, GATA2, PAX8, HOXB4</t>
+          <t>PAX8, MEF2A, POU1F1, MEIS1</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2768,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MEF2A, PGR, EGR1, JUND</t>
+          <t>NFIC, ZNF76</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2790,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MEF2C, SRF, RFX5, HDAC9</t>
+          <t>POU1F1, NR3C1, TP63, CEBPB</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2802,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JUNB, SOX2</t>
+          <t>LHX3, MAFF, ETV7</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2819,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NFRKB, JUND, KLF1, FOXQ1, ETV7</t>
+          <t>FOXQ1, ARNTL2, BARX2, PAX2</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2836,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FOSB, SHOX, PLAG1, ONECUT2, NR4A2</t>
+          <t>TFCP2L1, UHRF1, MLXIPL, SREBF2, E2F8</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2853,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IRF8, ONECUT2, MAX, CDX1</t>
+          <t>PER2, EOMES, FOXF1, PLAG1, FOXD3</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2875,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NCOR1, JUND</t>
+          <t>NFKB1, FOSL1, KLF4, HSF1, SLC2A4RG</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2897,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2913,12 +2914,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MEF2C, PITX1</t>
+          <t>TCF4, TOP2B</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2936,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GFI1, MYCN, ETV4</t>
+          <t>ATF5, POU2AF1, CRX</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2953,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PLAG1, TLE3, NAB2, CREB5</t>
+          <t>NAB2, NFKB2, MYBL2, HOXC10</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2970,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SHOX2, LHX2, SLA2</t>
+          <t>NR1I3, BHLHE41, HNF1A</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2982,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BATF, EN1</t>
+          <t>DLX5, DDIT3, TBX21, JUND</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3004,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NANOG, FOXP2, PRDM1, NFATC2</t>
+          <t>NAB2, GATA1, ETS2, RUNX1</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3021,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZFHX3, NR5A2, SOX17, RUNX3</t>
+          <t>RUNX2, TAL1, HDAC2, ETS1, ESR1</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3033,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ERF, GATA2, GATA3, ARID3A, RUNX3</t>
+          <t>BARD1, TEAD4</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3055,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HLX, PITX3, HDAC10</t>
+          <t>E2F5, UHRF1, RELB, ZBTB16</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3067,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HNF4G, TOP2B, TFAP2C, TBX5</t>
+          <t>NOTCH3, SNAI1, TFAP2C, NR0B2, RXRA</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3084,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FOXJ1</t>
+          <t>LIN28A, CEBPE</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3101,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WWTR1, TCF19, ONECUT1, ZIC1</t>
+          <t>TBX5, HNF1A, GLI1, GATA6</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3123,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDM4, FOXA1, KLF2, REST</t>
+          <t>PGR, GATA1, ETS1, LMO2</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3135,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESRRG, REL, GFI1, ZBTB16</t>
+          <t>TRIB3, JUN, CDX2, TFAP2A, GATA1</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3152,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LMO2, HNF1A, SPI1, TIAL1, HOXA1</t>
+          <t>NUPR1, MITF, SPI1</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MEF2B, NKX2-5, TOB1</t>
+          <t>HEY2, NHLH2</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3186,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STAT5A, BCL6, CIITA, ELK1, XBP1</t>
+          <t>HOXA11, GFI1, FOSL2</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3203,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KHDRBS1, TCF4, SPI1, COPS5, HIF3A</t>
+          <t>ZNF423, HSF2, GLI2, CEBPE, ETV6</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3220,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HIVEP2, SPDEF, FOXC2, REL</t>
+          <t>PARP1, HIF1A, IRF1, SP1</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3242,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JUND, HEYL, ELK1</t>
+          <t>JARID2, FOXG1, NR4A2, EIF2AK2</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3254,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAX, ESR1, ESR2, RUNX1</t>
+          <t>HSF4, HES6, ZNF143, ETV7</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3276,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EHF, TBX21, PAX2, GATA1</t>
+          <t>TFCP2, TBX21, PAX2, NR5A1</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3293,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ZIC1, SHOX2, SLA2</t>
+          <t>CRX, BRIP1, ONECUT2</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3310,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PPARD, NFE2, JUN, GLI1</t>
+          <t>NFIC, NFATC2</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3322,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CEBPA, ETV4, HOXA10, JUND, ONECUT2</t>
+          <t>BRIP1, ETV7</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3344,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HLX, ZFP36L1, FOXG1, ASCL1</t>
+          <t>RFX2, EIF2AK2, DBP, FOXG1, GATA6</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3356,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GATA6, SIX1, CDX1, FOXH1, GLI1</t>
+          <t>NR2E3, GATA1, GLI1, CDX1</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3378,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KLF12, DBP, SEC14L2</t>
+          <t>NR1I3, TFAP2A, MYCN, HNF4A</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3390,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IRF5, HIVEP2, FOSL2, NR2C2</t>
+          <t>HDAC2, FOSL2, MYCN</t>
         </is>
       </c>
     </row>
@@ -3406,12 +3407,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KLF9, EGR2, BACH2, KLF6, GATA6</t>
+          <t>DACH1, HOXA5, RELB</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3424,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MEF2C</t>
+          <t>LEF1, MEF2D, EIF2AK2, HLX, POU5F1</t>
         </is>
       </c>
     </row>
@@ -3440,12 +3441,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TSC22D3, NR1H4, ETV4, ZBTB7A</t>
+          <t>EBF3, EGR2, FOXO1, HOXA1</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3458,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZFHX3, ETV6, E2F8</t>
+          <t>GRHL1, BARD1, ETS2, GATA1</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3480,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GLI1, EGR1, TFAP2A</t>
+          <t>TCF4, EGR1, TFAP2A</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3497,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAML1, BHLHE41, ASXL1, TBX5, PITX2</t>
+          <t>NR1I2, EGR1, HNF4A</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3514,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HLX, NFIL3, CREB5, ONECUT2</t>
+          <t>ONECUT2, CEBPG, HOXA7, ZIC2</t>
         </is>
       </c>
     </row>
@@ -3525,12 +3526,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KLF6, TFAP2C</t>
+          <t>ARX, TP53BP1, CEBPE, TFAP2C, BARX2</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3543,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RBMX, SOX4, NR4A2, ETV7, FOXG1</t>
+          <t>ETS2, SPI1, EGR1, JUN, TP53</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3560,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UHRF1, SPDEF, HNRNPD</t>
+          <t>MYBL2, CREB5</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3577,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FOSL1, IRF1, PITX1, POU3F2</t>
+          <t>SMAD1, NAB2, SIX1</t>
         </is>
       </c>
     </row>
@@ -3593,12 +3594,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HLF, LHX4, ZIC1</t>
+          <t>HOXA11, NR4A2, TEAD4, MEIS1, PITX2</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3616,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ZNF143, HAND2, JARID2</t>
+          <t>STAT4, POU5F1, CREM, ETV1</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3633,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KLF12, PRDM1, KHSRP, EIF2AK2, HIF3A, ZIC2</t>
+          <t>DLX4, FOXF1, SRF, NFYB, MAFK</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3645,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ATF3, NR4A1, FOSL2</t>
+          <t>ASXL1, MAFF, ETV7</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3667,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JUNB, DDIT3, PAX2</t>
+          <t>PPARD, DDIT3, CIITA, FOXQ1</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3684,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E2F6, DDIT3, FOXG1, E2F5, ZFP36, CTCFL</t>
+          <t>CTCFL, FOXN1, E2F8, POU2AF1, TFAP2B</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3696,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MAF, CBX7, JUND, NKX3-1</t>
+          <t>FOXF1, RFX2, SHOX2</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3713,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USF2, JUND</t>
+          <t>IRF6, NAB2, PCGF2, ZFP36, ARNTL2</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3740,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -3761,7 +3762,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZNF383, DLX4, TBX5</t>
+          <t>ETV7, DLX4, FOXL1</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3774,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PAWR, HES1, PITX2, HOXA4</t>
+          <t>FOXN1, CRABP2, EOMES, ATF5, MCM2</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3791,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TNFAIP3, FOXG1</t>
+          <t>JUN, CEBPE, GATA1, EGR1</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3808,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IRF2, SOX2, HES1</t>
+          <t>FOXH1, GFI1, CDX2, SPDEF</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3830,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KLF12, HOXC6, LMO3, PAX2</t>
+          <t>CRABP2, LIMD1, HLX, ELK3</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3842,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JUN, ZFP36</t>
+          <t>ATF3, POU5F1, TBX5</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3859,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZNF202, TIAL1, DLX4</t>
+          <t>NFATC2, SOX9, RUNX3, LHX4, ETS1, ESR1</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3881,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TIAL1, FOXD3, ONECUT1, SLA2</t>
+          <t>BARD1, SIX1, FOXD3</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3893,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TLE3, HIC1, XBP1, CEBPD, GLI1, FLI1</t>
+          <t>KLF4, SMAD7, NR2F2, DLX4, GLI2, CEBPD</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3910,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DLX5, NKX2-3, ETV7, TOP2B, TFAP2C, TBX5</t>
+          <t>CDX2, RUNX1, KLF5</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3927,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UHRF1, CEBPE</t>
+          <t>NUPR1, TP63, CEBPE</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3949,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UHRF1, GATA1, PIR</t>
+          <t>JUNB, GLI1, GATA1</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3961,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDM4, TBX3</t>
+          <t>TRIB3, TBX3, FOXA1, FOXO4</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3978,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CRABP2, HIF3A, HNF1A, EBF3</t>
+          <t>HDAC1, TWIST1, CDX2</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3995,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EGR3, MSX1, REL</t>
+          <t>MEIS1, WWTR1, SPI1, SFPQ, CREB5</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4012,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PRDM1, TWIST2, UHRF1, REL, NKX2-5</t>
+          <t>POU2F3, TOB1, TEAD4, MLXIPL</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4034,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TIAL1, FOXL1, MXD1, ZNF267, NR2C2, FOSL2</t>
+          <t>HES1, FOSL2, PRDM1, XBP1</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4046,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TCF4, ERCC2, CEBPA, KHDRBS1, SPI1</t>
+          <t>RELB, GATA1</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4063,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HSF2, HOXB7, IRF2, TCF7L2</t>
+          <t>ZNF410, REL, SALL4</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4080,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FOXF1, SOX4, ZFP36, ETV7</t>
+          <t>MAFF, JUNB, NR4A1, ATF5</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4097,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STAT5A, TP63</t>
+          <t>TLE3, POU2AF1</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4114,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NFATC2, NR5A1, SATB1, DR1, NR0B2, GLI2</t>
+          <t>IRF6, TBX21, FOSL2, HNF1A</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4136,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RFX2, SLA2, CRABP2</t>
+          <t>EN1, CRX</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4148,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TRPS1, GLI1</t>
+          <t>MSC, ZEB1, ETV4, ZNF383</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4165,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FIGLA, EBF1, ZIC1, NR4A2</t>
+          <t>NR4A1, JUND, LMO4</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4182,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HOXC8, MXD1, MAFF, FOXG1, GATA6</t>
+          <t>ZNF383, FOXH1, NR0B2</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4199,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FOXM1, GATA1</t>
+          <t>NKX2-5, GFI1B, EAF1, ONECUT2</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4221,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ZNF300, E2F7, CDX1, RUNX2, SALL4, RUNX1</t>
+          <t>TIAL1, SP7, NAB2, ARNTL2, HOXA1</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4233,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MYCN, ETS1, PITX1, HOXB7, HEYL</t>
+          <t>MCM2, FOSL2, ID4, PER2</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4255,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TBX21, NANOG, CEBPZ, NR4A1</t>
+          <t>DBP, ZNF382, RAD51, PAX2</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4272,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PPARD, MEIS1, HOXC6, POU5F1, EIF2AK2</t>
+          <t>ISL1, EOMES, RFX3</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4289,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HOXC8, SIM2, SMURF2, CDX2, FOXF1</t>
+          <t>STAT4, GATA2, NR1H4</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4306,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZFP36, MEF2A, GATA1, FHL2</t>
+          <t>GLI3, BARD1, TWIST2</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4323,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PTTG1, EGR1</t>
+          <t>ZNF383, EGR1, CIITA, CREB5</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4340,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PITX2, DBP, NAB2</t>
+          <t>FOXP2, HOXA1, NR0B2, SOX17</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4357,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HLX, NFIL3, NR4A2, ONECUT2</t>
+          <t>NFIL3, TLE3, TFAP2C, MEF2B</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4369,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TWIST1, BRCA1</t>
+          <t>TRIM22, ETS2, CDX1, ZFP36</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4391,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MAML1, GATA6, NKX2-5, FOXF1</t>
+          <t>LHX2, EBF1, ETV7, NR4A2</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4408,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEY1, SPDEF</t>
+          <t>EHF, SPDEF, HEY1</t>
         </is>
       </c>
     </row>
@@ -4419,12 +4420,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>POU3F2, NR4A2, SIX1, EOMES</t>
+          <t>EGR1, GATA1, HNF4A</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4442,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TEAD4, NHLH2, HOXB1, TEAD1</t>
+          <t>SHOX2, NR4A2, TEAD4, HEY1, PITX2</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4459,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HOXD1, MSX2, OTX1, EOMES</t>
+          <t>IRF6, ETV7, HOXC6</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4471,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GLI3, SOX17, BRIP1</t>
+          <t>SRF, CEBPD, RBBP7</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4488,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.466666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ETV7, LMO3</t>
+          <t>MSC, NR4A1, FOSL2</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4505,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ETV7, SLA2, FOXJ1</t>
+          <t>ASXL1, BARX2, PAX2, FOXQ1</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4527,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KLF2, RBL1, IRF3, SREBF2</t>
+          <t>ETV7, FOSB, SREBF2, NKX2-5</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4539,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FOXL1, ZBTB16, SLC2A4RG</t>
+          <t>HOXD3, HLF, FOXD3, RFX2</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4556,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ZFP36, KDM2A, SP2</t>
+          <t>HIF1A, JUND, ABL1</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4583,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AgeIndex</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4599,12 +4600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZIC1, RUNX1, PITX1, PAX8</t>
+          <t>UHRF1, JUNB, ETV4, ATF3</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4617,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PTTG1, ETV4, NR2F2, PITX1</t>
+          <t>RUNX2, MYCN, ETV4</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4639,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JUND, RELB</t>
+          <t>DDIT3, CREB5, JUND</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4651,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DBP, LHX2, SLA2</t>
+          <t>E2F5, CIITA, HNF1A</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4668,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MXD1, POU5F1, LIMD1, PAX2</t>
+          <t>ETS1, NR1I2, GATA1, FOXM1</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4690,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>POU5F1, GATA1, TAL1</t>
+          <t>NAB2, PER2, SOX2, RUNX1</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4707,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BTAF1, HOXA1, ZNF335, ETV7</t>
+          <t>PER1, BCL6, ETS1, REL, ESR1</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4719,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ERF, GATA2, GATA3, ARID3A, RUNX3</t>
+          <t>LHX2, RUNX3, FOXP1, ARID3A</t>
         </is>
       </c>
     </row>
@@ -4735,12 +4736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TLE3, HIC1, XBP1, CEBPD, GLI1, FLI1</t>
+          <t>NFKB2, KLF8, CEBPD</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4758,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HIF3A, DLX5, ATRX, TBX5, ETV7, MAFB</t>
+          <t>ID3, TFAP2C, NR0B2, ZBTB16</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4770,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TLE3, SIX1, CEBPE</t>
+          <t>RUNX1, TP63, FOXO3</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4787,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WWTR1, TCF19, ONECUT1, ZIC1</t>
+          <t>HES1, TFAP2A</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4804,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GLIS3, DLX4, WWTR1, SHOX2</t>
+          <t>HNRNPD, ID3, TRIP6</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4826,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RELB, GFI1, ZBTB16</t>
+          <t>SATB2, DBP, TWIST1, TP63, PAX8</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4843,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEAT1, CREB5, NPAS2, UTF1</t>
+          <t>REL, MED15, SPI1, EGR3</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4855,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PRDM1, TWIST2, UHRF1, REL, NKX2-5</t>
+          <t>FOXN1, REL, CREB5, SRSF1, NUPR1</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4872,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MEF2B, TEAD1, XBP1, OTX2, FOSL2</t>
+          <t>PRDM1, NFIA, OTX2, XBP1</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4894,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NFIC, NFE2, IRF2, SPI1</t>
+          <t>ZNF383, GLI1, SOX17, SPI1</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4906,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.666666666666667</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOX2, CDX2, NUPR1</t>
+          <t>HLF, REL, RORC, FOXP2</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NFIC, ZFP36, HOPX, TCF7, NANOG</t>
+          <t>GCM1, JUND, RARG, NR4A1, HEYL</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4940,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RUNX1, SPDEF, HSF4, NR5A2, TP63</t>
+          <t>TOP2B, PAX3</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MYF6, GATA4, TFDP3, LMO2</t>
+          <t>FOSL2, NR2E3, SALL3, CITED2</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4974,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>POU5F1, CREB5, ETV4, PPARG</t>
+          <t>FIGLA, FOXD3, SLA2, ZIC1</t>
         </is>
       </c>
     </row>
@@ -4990,12 +4991,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TFAP2A, IRF3, MITF, PITX1</t>
+          <t>GLI1, NFE2</t>
         </is>
       </c>
     </row>
@@ -5007,12 +5008,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MTA3, CREB5, CDX1, EOMES</t>
+          <t>KLF12, ETV7</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5025,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RELB, MXD1, CDX1</t>
+          <t>RELB, CREB5, HEYL</t>
         </is>
       </c>
     </row>
@@ -5041,12 +5042,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TFCP2L1, EED, EOMES, EAF1, SIX1</t>
+          <t>GZF1, DBP, GATA1, CDX1, NANOG</t>
         </is>
       </c>
     </row>
@@ -5058,12 +5059,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KLF5, CDX1, RUNX1, REL</t>
+          <t>MCM2, HOXA1, SOX4</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5076,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IRF5, CEBPG, FOSL2, NR2C2</t>
+          <t>YY1, PITX1, SP1, FOSL2</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5098,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KLF9, EGR2, BACH2, KLF6, GATA6</t>
+          <t>MAFG, ZIC1, EBF3, HOXA5</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5115,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CREB5, RELB, SALL4</t>
+          <t>TBX21, GATA6, ZFP36, STAT4, TNFAIP3, IRF1</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5132,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CDX1, NOTCH3, FOXO1, NR1H4, SOX4, GLI1</t>
+          <t>EHF, ZEB1, GATA2, CDX2</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5144,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZNF300, PAWR, GLI3, E2F8</t>
+          <t>E2F7, NR2C2, SOX17, HOXC13</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5161,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FOXJ1, NAB2, PAX2, CREB5</t>
+          <t>PAX2, GLI1, EGR1, TFAP2A</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5183,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LMO3, NAB2, PLAG1, PITX2, HLF</t>
+          <t>FOXQ1, HOXA4, FOXF2</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5195,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HLX, NFIL3, CREB5, ONECUT2</t>
+          <t>NFIL3, POU1F1, JDP2</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5212,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BACH1, HOXA1, HIF3A</t>
+          <t>TRIP6, HNF4G, CEBPE, HOXA1</t>
         </is>
       </c>
     </row>
@@ -5228,12 +5229,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AHR, GLI2, IRF8, EGR1, CEBPB</t>
+          <t>BCL6, WDR5, GLI2, NAB2, PML</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5246,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SPIB, CDX1, HIF3A, CREB5</t>
+          <t>TCF7, PITX1</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5263,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GATA1, ZFP36, PITX1</t>
+          <t>FOSL1, NR4A1, FOS</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5280,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TEAD4, NHLH2, HOXB1, TEAD1</t>
+          <t>NFIA, RARG, BCL6, NFIL3</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EGR1, PGR, FOS, IRF1</t>
+          <t>LMX1B, ONECUT2, IRF6, NR4A2</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5319,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HDAC7, HDAC9, POLR1A, CREM, PGR, RFX5</t>
+          <t>ZEB2, TP63, CEBPB, HEYL, HDAC9</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5331,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.533333333333333</t>
+          <t>0.466666666666667</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HIVEP2, FOSL2, ELF3, LMO3, POU1F1</t>
+          <t>NR5A2, FOSL2</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5353,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FOXJ1, SLA2, DDIT3, SOX2, JUND</t>
+          <t>RELB, PAX2, SOX2, ETV7</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5370,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FOSB, SHOX, PLAG1, ONECUT2, NR4A2</t>
+          <t>KLF2, FOXA1, PLAG1, E2F8</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5387,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MLXIPL, MSX1, ONECUT1</t>
+          <t>BHLHE41, PAX3, PLAG1</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5399,855 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.666666666666667</t>
+          <t>0.533333333333333</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JUND, HES1, POU5F1, ABL1</t>
+          <t>NFKB1, POU2F1, SOX6, FOSL1, KLF4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tissue</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gene_Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adipose_subcutaneous</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PITX1, NANOG, DBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adipose_visceral_omentum</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BHLHE41, CBX8, PITX1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adrenal_gland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>JUN, CEBPE, GATA1, EGR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>artery_aorta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FOXH1, GFI1, CDX2, SPDEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>artery_coronary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HOXC6, SHOX, ONECUT2, PITX2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>artery_tibial</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETS2, GATA1, NR1I2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>brain_amygdala</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HOXB7, CREB5, RUNX1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>brain_anterior_cingulate_cortex_ba24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BARD1, DLX4, NOTCH3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>brain_caudate_basal_ganglia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BARD1, CEBPD, E2F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>brain_cerebellar_hemisphere</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>KLF15, TOP2B, TFAP2C, TBX5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>brain_cerebellum</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HIF3A, TBX5, NR4A2, NR0B2, MAFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>brain_cortex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GLI1, NUPR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>brain_frontal_cortex_ba9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TRIB3, TBX3, FOXA1, FOXO4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>brain_hippocampus</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SATB2, DBP, TWIST1, TP63, PAX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>brain_hypothalamus</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SPI1, ANKRD1, REL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>brain_nucleus_accumbens_basal ganglia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PAX8, HIF3A, CEBPE, SFPQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>brain_putamen_basal_ganglia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BCL6, E2F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>brain_spinal_cord_cervical_c-1)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NFE2, SPI1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>brain_substantia_nigra</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HLF, REL, RORC, FOXP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>breast_mammary_tissue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RARB, JUND, NR4A1, HEYL, EGR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cells_cultured_fibroblasts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HSF4, HES6, ZNF143, ETV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cells_ebv-transformed_lymphocytes</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FOSL2, NR2E3, SALL3, CITED2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>colon_sigmoid</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TBX21, FIGLA, NOTCH3, TFAP2A, PPARG, POU5F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>colon_transverse</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOX2, NFIL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>esophagus_gastroesophageal_junction</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HOXA10, CREB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>esophagus_mucosa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RFX2, EIF2AK2, DBP, FOXG1, GATA6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>esophagus_muscularis</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TP63, GLI1, NANOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>heart_atrial_appendage</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RUNX1, MXD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>heart_left_ventricle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FOSL2, ETS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>liver</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MAFG, ZIC1, EBF3, HOXA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>lung</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EOMES, GLIS3, SLA2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>minor_salivary_gland</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EOMES, HOXA1, FOXF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>muscle_skeletal</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETS2, AHR, GATA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>nerve_tibial</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PAX2, EOMES, HOXA4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ovary</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TBX5, OTX1, HOXA4, FOXQ1, PITX2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>pancreas</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HLX, NFIL3, ONECUT2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pituitary</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BACH1, HIF3A, HOXA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>prostate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GATA6, EOMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>skin_not_sun_exposed_suprapubic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HEY1, SPDEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>skin_sun_exposed_lower_leg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PITX1, UHRF1, GATA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>small_intestine_terminal_ileum</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CREB5, HLX, TEAD4, DLX3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>spleen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LMX1B, ONECUT2, IRF6, NR4A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stomach</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SRF, CEBPD, NOTCH3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>testis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MAFF, ASXL1, ETV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>thyroid</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SP7, PAX2, KLF1, FOXQ1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>uterus</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ONECUT2, FOSB, TFAP2B, HLX, E2F8, SHOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>vagina</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0.666666666666667</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FOXF1, FOXN1, HOXD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>whole_blood</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SLC2A4RG, MAFF, ZNF143</t>
         </is>
       </c>
     </row>
